--- a/output_files/ensemble_model_metrics.xlsx
+++ b/output_files/ensemble_model_metrics.xlsx
@@ -1,21 +1,134 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Clarke v Steenderen\Documents\Rosali\figures\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9F118C-25C4-4139-8A62-22E753779EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-21720" yWindow="1530" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
+  <si>
+    <t>algo</t>
+  </si>
+  <si>
+    <t>KAPPA</t>
+  </si>
+  <si>
+    <t>ROC</t>
+  </si>
+  <si>
+    <t>TSS</t>
+  </si>
+  <si>
+    <t>GBM</t>
+  </si>
+  <si>
+    <t>0.73 ± 0.09</t>
+  </si>
+  <si>
+    <t>0.95 ± 0.03</t>
+  </si>
+  <si>
+    <t>0.79 ± 0.07</t>
+  </si>
+  <si>
+    <t>GLM</t>
+  </si>
+  <si>
+    <t>0.75 ± 0.08</t>
+  </si>
+  <si>
+    <t>0.84 ± 0.05</t>
+  </si>
+  <si>
+    <t>MARS</t>
+  </si>
+  <si>
+    <t>0.71 ± 0.08</t>
+  </si>
+  <si>
+    <t>0.78 ± 0.07</t>
+  </si>
+  <si>
+    <t>MAXNET</t>
+  </si>
+  <si>
+    <t>0.7 ± 0.08</t>
+  </si>
+  <si>
+    <t>0.86 ± 0.06</t>
+  </si>
+  <si>
+    <t>RF</t>
+  </si>
+  <si>
+    <t>0.75 ± 0.09</t>
+  </si>
+  <si>
+    <t>0.75 ± 0.1</t>
+  </si>
+  <si>
+    <t>FDA</t>
+  </si>
+  <si>
+    <t>0.66 ± 0.11</t>
+  </si>
+  <si>
+    <t>0.9 ± 0.05</t>
+  </si>
+  <si>
+    <t>0.79 ± 0.08</t>
+  </si>
+  <si>
+    <t>GAM</t>
+  </si>
+  <si>
+    <t>0.68 ± 0.1</t>
+  </si>
+  <si>
+    <t>0.8 ± 0.08</t>
+  </si>
+  <si>
+    <t>CTA</t>
+  </si>
+  <si>
+    <t>0.7 ± 0.07</t>
+  </si>
+  <si>
+    <t>0.89 ± 0.04</t>
+  </si>
+  <si>
+    <t>ANN</t>
+  </si>
+  <si>
+    <t>0.42 ± 0.22</t>
+  </si>
+  <si>
+    <t>0.77 ± 0.09</t>
+  </si>
+  <si>
+    <t>0.54 ± 0.19</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +176,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +228,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +262,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +297,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,228 +473,152 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="24.77734375" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>algo</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>KAPPA</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ROC</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>TSS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>RF</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>0.883 (± 0.124)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1 (± 0)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.834 (± 0.176)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MARS</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0.873 (± 0.136)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0.969 (± 0.089)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.851 (± 0.165)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>GLM</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0.883 (± 0.124)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0.916 (± 0.088)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.834 (± 0.176)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>MAXNET</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.929 (± 0.114)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.903 (± 0.157)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.9 (± 0.161)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>GAM</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0.833 (± 0.176)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0.896 (± 0.113)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.792 (± 0.227)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>FDA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.906 (± 0.121)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.895 (± 0.141)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.867 (± 0.172)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ANN</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>0.589 (± 0.105)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0.872 (± 0.079)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.744 (± 0.158)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>GBM</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>0.588 (± 0.173)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0.864 (± 0.116)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0.541 (± 0.166)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CTA</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>0.717 (± 0.208)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0.817 (± 0.123)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.633 (± 0.246)</t>
-        </is>
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/output_files/ensemble_model_metrics.xlsx
+++ b/output_files/ensemble_model_metrics.xlsx
@@ -1,134 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Clarke v Steenderen\Documents\Rosali\figures\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9F118C-25C4-4139-8A62-22E753779EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="1530" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
-  <si>
-    <t>algo</t>
-  </si>
-  <si>
-    <t>KAPPA</t>
-  </si>
-  <si>
-    <t>ROC</t>
-  </si>
-  <si>
-    <t>TSS</t>
-  </si>
-  <si>
-    <t>GBM</t>
-  </si>
-  <si>
-    <t>0.73 ± 0.09</t>
-  </si>
-  <si>
-    <t>0.95 ± 0.03</t>
-  </si>
-  <si>
-    <t>0.79 ± 0.07</t>
-  </si>
-  <si>
-    <t>GLM</t>
-  </si>
-  <si>
-    <t>0.75 ± 0.08</t>
-  </si>
-  <si>
-    <t>0.84 ± 0.05</t>
-  </si>
-  <si>
-    <t>MARS</t>
-  </si>
-  <si>
-    <t>0.71 ± 0.08</t>
-  </si>
-  <si>
-    <t>0.78 ± 0.07</t>
-  </si>
-  <si>
-    <t>MAXNET</t>
-  </si>
-  <si>
-    <t>0.7 ± 0.08</t>
-  </si>
-  <si>
-    <t>0.86 ± 0.06</t>
-  </si>
-  <si>
-    <t>RF</t>
-  </si>
-  <si>
-    <t>0.75 ± 0.09</t>
-  </si>
-  <si>
-    <t>0.75 ± 0.1</t>
-  </si>
-  <si>
-    <t>FDA</t>
-  </si>
-  <si>
-    <t>0.66 ± 0.11</t>
-  </si>
-  <si>
-    <t>0.9 ± 0.05</t>
-  </si>
-  <si>
-    <t>0.79 ± 0.08</t>
-  </si>
-  <si>
-    <t>GAM</t>
-  </si>
-  <si>
-    <t>0.68 ± 0.1</t>
-  </si>
-  <si>
-    <t>0.8 ± 0.08</t>
-  </si>
-  <si>
-    <t>CTA</t>
-  </si>
-  <si>
-    <t>0.7 ± 0.07</t>
-  </si>
-  <si>
-    <t>0.89 ± 0.04</t>
-  </si>
-  <si>
-    <t>ANN</t>
-  </si>
-  <si>
-    <t>0.42 ± 0.22</t>
-  </si>
-  <si>
-    <t>0.77 ± 0.09</t>
-  </si>
-  <si>
-    <t>0.54 ± 0.19</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -176,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -228,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -262,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -297,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -473,152 +350,228 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="24.77734375" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>33</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>algo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>KAPPA</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ROC</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>TSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.883 (± 0.124)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1 (± 0)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.834 (± 0.176)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MARS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.873 (± 0.136)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.969 (± 0.089)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.851 (± 0.165)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GLM</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.883 (± 0.124)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.916 (± 0.088)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.834 (± 0.176)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MAXNET</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.929 (± 0.114)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.903 (± 0.157)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.9 (± 0.161)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GAM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.833 (± 0.176)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.896 (± 0.113)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.792 (± 0.227)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FDA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.906 (± 0.121)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.895 (± 0.141)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.867 (± 0.172)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ANN</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.589 (± 0.105)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.872 (± 0.079)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.744 (± 0.158)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GBM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.588 (± 0.173)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.864 (± 0.116)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.541 (± 0.166)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CTA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.717 (± 0.208)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.817 (± 0.123)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.633 (± 0.246)</t>
+        </is>
       </c>
     </row>
   </sheetData>
